--- a/Result/profitability/4161.xlsx
+++ b/Result/profitability/4161.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.61</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38625</v>
+        <v>0.425</v>
       </c>
       <c r="N2" t="n">
-        <v>30.7375</v>
+        <v>30.23375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.35125</v>
+        <v>0.36375</v>
       </c>
       <c r="N3" t="n">
-        <v>30.35375</v>
+        <v>29.53125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -8431,6 +8431,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4161</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>238</v>
+      </c>
+      <c r="D64" t="n">
+        <v>174</v>
+      </c>
+      <c r="E64" t="n">
+        <v>64</v>
+      </c>
+      <c r="F64" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="G64" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6.15%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>29</v>
+      </c>
+      <c r="J64" t="n">
+        <v>44</v>
+      </c>
+      <c r="K64" t="n">
+        <v>39</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.3925000000000001</v>
+      </c>
+      <c r="N64" t="n">
+        <v>29.57375</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.07958833619210981</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>-0.3300000000000018</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>-0.01215022091310758</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
